--- a/jira_export_2026-09-08.xlsx
+++ b/jira_export_2026-09-08.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>10,449 €</t>
+          <t>10,730 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -767,7 +767,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>7,092 €</t>
+          <t>7,373 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>120 h</t>
+          <t>122 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -886,7 +886,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>272</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P99"/>
+  <dimension ref="A1:P100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1877,7 +1877,7 @@
         <v>2</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>43</v>
       </c>
       <c r="P16" s="15" t="n">
-        <v>28.67</v>
+        <v>19.11</v>
       </c>
     </row>
     <row r="17">
@@ -5350,12 +5350,12 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
@@ -5401,19 +5401,19 @@
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>130</v>
-      </c>
-      <c r="O65" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O65" s="12" t="n">
+        <v>281</v>
       </c>
       <c r="P65" s="12" t="n">
         <v>0</v>
@@ -5422,12 +5422,12 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
@@ -5437,12 +5437,12 @@
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
@@ -5473,16 +5473,16 @@
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O66" s="16" t="n">
         <v>0</v>
@@ -5494,12 +5494,12 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -5534,27 +5534,27 @@
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K67" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O67" s="16" t="n">
         <v>0</v>
@@ -5566,32 +5566,32 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
@@ -5601,32 +5601,32 @@
       </c>
       <c r="H68" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
         <v>8</v>
       </c>
       <c r="K68" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>690</v>
+        <v>140</v>
       </c>
       <c r="O68" s="16" t="n">
         <v>0</v>
@@ -5638,27 +5638,27 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
@@ -5678,27 +5678,27 @@
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
         <v>8</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>187.5</v>
+        <v>690</v>
       </c>
       <c r="O69" s="16" t="n">
         <v>0</v>
@@ -5761,16 +5761,16 @@
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O70" s="16" t="n">
         <v>0</v>
@@ -5782,32 +5782,32 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
@@ -5817,35 +5817,35 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K71" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" s="12" t="n">
-        <v>362.5</v>
+        <v>787.5</v>
+      </c>
+      <c r="O71" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P71" s="12" t="n">
         <v>0</v>
@@ -5854,30 +5854,32 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E72" s="14" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E72" s="14" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
@@ -5887,35 +5889,35 @@
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K72" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O72" s="15" t="n">
-        <v>0</v>
+        <v>362.5</v>
       </c>
       <c r="P72" s="15" t="n">
         <v>0</v>
@@ -5924,12 +5926,12 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
@@ -5939,13 +5941,11 @@
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E73" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="n">
+        <v/>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
@@ -5964,23 +5964,23 @@
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
@@ -6119,12 +6119,12 @@
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
@@ -6191,12 +6191,12 @@
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
@@ -6263,18 +6263,18 @@
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O77" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P77" s="12" t="n">
@@ -6284,12 +6284,12 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
@@ -6299,11 +6299,13 @@
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E78" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E78" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
@@ -6317,34 +6319,34 @@
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K78" s="14" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="15" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O78" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P78" s="15" t="n">
@@ -6354,12 +6356,12 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
@@ -6369,34 +6371,48 @@
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>CD74</t>
-        </is>
-      </c>
-      <c r="E79" s="11" t="inlineStr">
-        <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F79" s="11" t="inlineStr"/>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F79" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G79" s="11" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H79" s="11" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H79" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L79" s="11" t="inlineStr"/>
-      <c r="M79" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L79" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27642</t>
+        </is>
+      </c>
+      <c r="M79" s="11" t="inlineStr">
+        <is>
+          <t>00143935</t>
+        </is>
+      </c>
       <c r="N79" s="12" t="n">
         <v>0</v>
       </c>
@@ -6410,12 +6426,12 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
@@ -6425,48 +6441,34 @@
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
-        </is>
-      </c>
-      <c r="E80" s="14" t="n">
-        <v/>
-      </c>
-      <c r="F80" s="14" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E80" s="14" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F80" s="14" t="inlineStr"/>
       <c r="G80" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H80" s="14" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H80" s="14" t="inlineStr"/>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K80" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L80" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-26814</t>
-        </is>
-      </c>
-      <c r="M80" s="14" t="inlineStr">
-        <is>
-          <t>00142941</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L80" s="14" t="inlineStr"/>
+      <c r="M80" s="14" t="inlineStr"/>
       <c r="N80" s="15" t="n">
         <v>0</v>
       </c>
@@ -6480,12 +6482,12 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
@@ -6495,7 +6497,7 @@
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
@@ -6513,34 +6515,34 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O81" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P81" s="12" t="n">
@@ -6550,12 +6552,12 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
@@ -6565,7 +6567,7 @@
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E82" s="14" t="n">
@@ -6588,29 +6590,29 @@
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" s="15" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O82" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P82" s="15" t="n">
@@ -6620,12 +6622,12 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23750</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>MEL - LITTERALIS x AXION</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
@@ -6635,13 +6637,11 @@
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
-        </is>
-      </c>
-      <c r="E83" s="11" t="inlineStr">
-        <is>
-          <t>AXION</t>
-        </is>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="n">
+        <v/>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
@@ -6650,33 +6650,33 @@
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>08/08/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
         <v>13</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27033</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>497304</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
@@ -6692,26 +6692,28 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-23750</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>MEL - LITTERALIS x AXION</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
-        </is>
-      </c>
-      <c r="E84" s="14" t="n">
-        <v/>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
+        </is>
+      </c>
+      <c r="E84" s="14" t="inlineStr">
+        <is>
+          <t>AXION</t>
+        </is>
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
@@ -6720,7 +6722,7 @@
       </c>
       <c r="G84" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H84" s="14" t="inlineStr">
@@ -6730,29 +6732,29 @@
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>08/08/2025</t>
         </is>
       </c>
       <c r="J84" s="14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K84" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27033</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>497304</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
-        <v>401</v>
-      </c>
-      <c r="O84" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P84" s="15" t="n">
@@ -6762,12 +6764,12 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
@@ -6777,7 +6779,7 @@
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E85" s="11" t="n">
@@ -6795,34 +6797,34 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O85" s="12" t="n">
+        <v>401</v>
+      </c>
+      <c r="O85" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P85" s="12" t="n">
@@ -6832,22 +6834,22 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E86" s="14" t="n">
@@ -6865,28 +6867,28 @@
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J86" s="14" t="n">
         <v>17</v>
       </c>
       <c r="K86" s="14" t="n">
-        <v>0.5</v>
+        <v>3.25</v>
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
@@ -6902,22 +6904,22 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E87" s="11" t="n">
@@ -6940,29 +6942,29 @@
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
         <v>17</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
-        <v>230</v>
-      </c>
-      <c r="O87" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P87" s="12" t="n">
@@ -6972,22 +6974,22 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E88" s="14" t="n">
@@ -7005,34 +7007,34 @@
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K88" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28215</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>458306</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" s="15" t="n">
+        <v>230</v>
+      </c>
+      <c r="O88" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P88" s="15" t="n">
@@ -7091,12 +7093,12 @@
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28214</t>
+          <t>PDMDEP-28215</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>458286</t>
+          <t>458306</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
@@ -7112,12 +7114,12 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
@@ -7127,7 +7129,7 @@
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E90" s="14" t="n">
@@ -7140,27 +7142,35 @@
       </c>
       <c r="G90" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J90" s="14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K90" s="14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L90" s="14" t="inlineStr"/>
-      <c r="M90" s="14" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L90" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28214</t>
+        </is>
+      </c>
+      <c r="M90" s="14" t="inlineStr">
+        <is>
+          <t>458286</t>
+        </is>
+      </c>
       <c r="N90" s="15" t="n">
         <v>0</v>
       </c>
@@ -7174,22 +7184,22 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E91" s="11" t="n">
@@ -7207,7 +7217,7 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
@@ -7219,7 +7229,7 @@
         <v>21</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="L91" s="11" t="inlineStr"/>
       <c r="M91" s="11" t="inlineStr"/>
@@ -7236,22 +7246,22 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E92" s="14" t="n">
@@ -7259,44 +7269,36 @@
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G92" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J92" s="14" t="n">
         <v>21</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M92" s="14" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>3.08</v>
+      </c>
+      <c r="L92" s="14" t="inlineStr"/>
+      <c r="M92" s="14" t="inlineStr"/>
       <c r="N92" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="O92" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="15" t="n">
@@ -7306,22 +7308,22 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E93" s="11" t="n">
@@ -7329,7 +7331,7 @@
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr">
@@ -7339,12 +7341,12 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
@@ -7355,16 +7357,16 @@
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
-        <v>557.145</v>
+        <v>240</v>
       </c>
       <c r="O93" s="16" t="n">
         <v>0</v>
@@ -7376,22 +7378,22 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E94" s="14" t="n">
@@ -7404,31 +7406,39 @@
       </c>
       <c r="G94" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H94" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K94" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L94" s="14" t="inlineStr"/>
-      <c r="M94" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L94" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M94" s="14" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N94" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O94" s="15" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O94" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P94" s="15" t="n">
@@ -7438,22 +7448,22 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13128</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E95" s="11" t="n">
@@ -7466,35 +7476,27 @@
       </c>
       <c r="G95" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L95" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M95" s="11" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L95" s="11" t="inlineStr"/>
+      <c r="M95" s="11" t="inlineStr"/>
       <c r="N95" s="12" t="n">
         <v>0</v>
       </c>
@@ -7508,22 +7510,22 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E96" s="14" t="n">
@@ -7536,23 +7538,35 @@
       </c>
       <c r="G96" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H96" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H96" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
         <v>36</v>
       </c>
       <c r="K96" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L96" s="14" t="inlineStr"/>
-      <c r="M96" s="14" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L96" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M96" s="14" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N96" s="15" t="n">
         <v>0</v>
       </c>
@@ -7566,24 +7580,26 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C97" s="11" t="inlineStr"/>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C97" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E97" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CD 56 MORBIHAN</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="n">
+        <v/>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
@@ -7595,21 +7611,17 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H97" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H97" s="11" t="inlineStr"/>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
         <v>36</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>2.75</v>
+        <v>0.5</v>
       </c>
       <c r="L97" s="11" t="inlineStr"/>
       <c r="M97" s="11" t="inlineStr"/>
@@ -7626,89 +7638,149 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr"/>
       <c r="D98" s="14" t="inlineStr">
         <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E98" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F98" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G98" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H98" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I98" s="14" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J98" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="K98" s="14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L98" s="14" t="inlineStr"/>
+      <c r="M98" s="14" t="inlineStr"/>
+      <c r="N98" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1270</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
           <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
-      <c r="E98" s="14" t="inlineStr"/>
-      <c r="F98" s="14" t="inlineStr">
+      <c r="C99" s="11" t="inlineStr"/>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr"/>
+      <c r="F99" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G98" s="14" t="inlineStr">
+      <c r="G99" s="11" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H98" s="14" t="inlineStr"/>
-      <c r="I98" s="14" t="inlineStr">
+      <c r="H99" s="11" t="inlineStr"/>
+      <c r="I99" s="11" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="J98" s="14" t="n">
+      <c r="J99" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="K98" s="14" t="n">
+      <c r="K99" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="L98" s="14" t="inlineStr">
+      <c r="L99" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-33362</t>
         </is>
       </c>
-      <c r="M98" s="14" t="inlineStr">
+      <c r="M99" s="11" t="inlineStr">
         <is>
           <t>00167140</t>
         </is>
       </c>
-      <c r="N98" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="17" t="inlineStr">
+      <c r="N99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B99" s="17" t="inlineStr"/>
-      <c r="C99" s="17" t="inlineStr"/>
-      <c r="D99" s="17" t="inlineStr"/>
-      <c r="E99" s="17" t="inlineStr"/>
-      <c r="F99" s="17" t="inlineStr"/>
-      <c r="G99" s="17" t="inlineStr"/>
-      <c r="H99" s="17" t="inlineStr"/>
-      <c r="I99" s="17" t="inlineStr"/>
-      <c r="J99" s="17" t="inlineStr"/>
-      <c r="K99" s="17" t="inlineStr"/>
-      <c r="L99" s="17" t="inlineStr"/>
-      <c r="M99" s="17" t="inlineStr"/>
-      <c r="N99" s="18" t="n">
+      <c r="B100" s="17" t="inlineStr"/>
+      <c r="C100" s="17" t="inlineStr"/>
+      <c r="D100" s="17" t="inlineStr"/>
+      <c r="E100" s="17" t="inlineStr"/>
+      <c r="F100" s="17" t="inlineStr"/>
+      <c r="G100" s="17" t="inlineStr"/>
+      <c r="H100" s="17" t="inlineStr"/>
+      <c r="I100" s="17" t="inlineStr"/>
+      <c r="J100" s="17" t="inlineStr"/>
+      <c r="K100" s="17" t="inlineStr"/>
+      <c r="L100" s="17" t="inlineStr"/>
+      <c r="M100" s="17" t="inlineStr"/>
+      <c r="N100" s="18" t="n">
         <v>47526.995</v>
       </c>
-      <c r="O99" s="18" t="n">
-        <v>10448.55</v>
-      </c>
-      <c r="P99" s="18" t="n">
-        <v>148.59</v>
+      <c r="O100" s="18" t="n">
+        <v>10729.55</v>
+      </c>
+      <c r="P100" s="18" t="n">
+        <v>150.44</v>
       </c>
     </row>
   </sheetData>
@@ -7808,6 +7880,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId95"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8565,16 +8638,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>37.5</v>
+        <v>38.25</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>9.83</v>
+        <v>10.08</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>5.75</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>53.08</v>
+        <v>54.08</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>7.17</v>
@@ -8584,7 +8657,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.3%</t>
         </is>
       </c>
     </row>
@@ -8711,19 +8784,19 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>366651</v>
+        <v>396735</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>132859</v>
+        <v>166191</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>233792</v>
+        <v>230544</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>142637</v>
+        <v>141521</v>
       </c>
       <c r="F5" s="24" t="n">
-        <v>21179</v>
+        <v>19046</v>
       </c>
       <c r="G5" s="24" t="n">
         <v>24521</v>
@@ -8745,10 +8818,10 @@
         <v>102379</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>85362</v>
+        <v>87495</v>
       </c>
       <c r="F6" s="25" t="n">
-        <v>11307</v>
+        <v>9175</v>
       </c>
       <c r="G6" s="25" t="n">
         <v>3185</v>
@@ -8761,16 +8834,16 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>201296</v>
+        <v>231380</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>69883</v>
+        <v>103215</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>131412</v>
+        <v>128164</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>57275</v>
+        <v>54027</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>9871</v>
@@ -8790,13 +8863,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="37" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -8814,7 +8887,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 6 commande(s)</t>
+          <t>Épics créées ce mois — 9 commande(s)</t>
         </is>
       </c>
     </row>
@@ -8869,22 +8942,22 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35478</t>
+          <t>PDMDEP-35532</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35469</t>
+          <t>PDMDEP-35518</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VENCE</t>
+          <t>COMMUNE DE PRIVAS</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -8897,39 +8970,31 @@
           <t>Migration</t>
         </is>
       </c>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="H5" s="14" t="inlineStr">
-        <is>
-          <t>00180643</t>
-        </is>
-      </c>
+      <c r="G5" s="14" t="inlineStr"/>
+      <c r="H5" s="14" t="inlineStr"/>
       <c r="I5" s="25" t="n">
-        <v>6285</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35410</t>
+          <t>PDMDEP-35478</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35401</t>
+          <t>PDMDEP-35469</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
+          <t>COMMUNE DE VENCE</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -8949,22 +9014,22 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>00173074</t>
+          <t>00180643</t>
         </is>
       </c>
       <c r="I6" s="26" t="n">
-        <v>1200</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35392</t>
+          <t>PDMDEP-35410</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35385</t>
+          <t>PDMDEP-35401</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
@@ -8974,7 +9039,7 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ROUEN</t>
+          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -8994,42 +9059,42 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>00179700</t>
+          <t>00173074</t>
         </is>
       </c>
       <c r="I7" s="25" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35511</t>
+          <t>PDMDEP-35392</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35504</t>
+          <t>PDMDEP-35385</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>[TEST]</t>
+          <t>COMMUNE DE ROUEN</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -9039,32 +9104,32 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>0015489263</t>
+          <t>00179700</t>
         </is>
       </c>
       <c r="I8" s="26" t="n">
-        <v>0</v>
+        <v>28915.01</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35464</t>
+          <t>PDMDEP-35576</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35460</t>
+          <t>PDMDEP-35572</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -9084,119 +9149,254 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>00180631</t>
+          <t>00180891</t>
         </is>
       </c>
       <c r="I9" s="25" t="n">
-        <v>455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-35567</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35561</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>00180878</t>
+        </is>
+      </c>
+      <c r="I10" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35511</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35504</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>[TEST]</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>0015489263</t>
+        </is>
+      </c>
+      <c r="I11" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35464</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35460</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>00180631</t>
+        </is>
+      </c>
+      <c r="I12" s="26" t="n">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
           <t>PDMDEP-35439</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>PDMDEP-35435</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>03/09/2026</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F13" s="14" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="H13" s="14" t="inlineStr">
         <is>
           <t>00180506</t>
         </is>
       </c>
-      <c r="I10" s="26" t="n">
+      <c r="I13" s="25" t="n">
         <v>3974</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n"/>
-      <c r="C11" s="17" t="n"/>
-      <c r="D11" s="17" t="n"/>
-      <c r="E11" s="17" t="n"/>
-      <c r="F11" s="17" t="n"/>
-      <c r="G11" s="17" t="n"/>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t>6 commande(s)</t>
-        </is>
-      </c>
-      <c r="I11" s="24" t="n">
-        <v>11914</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="17" t="n"/>
+      <c r="G14" s="17" t="n"/>
+      <c r="H14" s="17" t="inlineStr">
+        <is>
+          <t>9 commande(s)</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="n">
+        <v>42279</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>dont Littéralis</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n"/>
-      <c r="C12" s="17" t="n"/>
-      <c r="D12" s="17" t="n"/>
-      <c r="E12" s="17" t="n"/>
-      <c r="F12" s="17" t="n"/>
-      <c r="G12" s="17" t="n"/>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t>3 commande(s)</t>
-        </is>
-      </c>
-      <c r="I12" s="24" t="n">
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
+      <c r="G15" s="17" t="n"/>
+      <c r="H15" s="17" t="inlineStr">
+        <is>
+          <t>5 commande(s)</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="n">
         <v>4429</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>dont GEODP</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n"/>
-      <c r="C13" s="17" t="n"/>
-      <c r="D13" s="17" t="n"/>
-      <c r="E13" s="17" t="n"/>
-      <c r="F13" s="17" t="n"/>
-      <c r="G13" s="17" t="n"/>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>3 commande(s)</t>
-        </is>
-      </c>
-      <c r="I13" s="24" t="n">
-        <v>7485</v>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="17" t="n"/>
+      <c r="F16" s="17" t="n"/>
+      <c r="G16" s="17" t="n"/>
+      <c r="H16" s="17" t="inlineStr">
+        <is>
+          <t>4 commande(s)</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="n">
+        <v>37850</v>
       </c>
     </row>
   </sheetData>
@@ -9210,7 +9410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -9231,7 +9431,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1 clôture(s) : 1 projet(s), 0 rework</t>
+          <t>2 clôture(s) : 2 projet(s), 0 rework</t>
         </is>
       </c>
     </row>
@@ -9271,59 +9471,89 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
+          <t>PDMDEP-31319</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simpl</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE LARMOR PLAGE</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
           <t>PDMDEP-33699</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>[CD 35)] - Montée de version Littéralis - 1 journée d'assist</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="F5" s="14" t="n">
+      <c r="F6" s="11" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n"/>
-      <c r="C7" s="17" t="n"/>
-      <c r="D7" s="17" t="n"/>
-      <c r="E7" s="17" t="n"/>
-      <c r="F7" s="17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n"/>
-      <c r="C8" s="27" t="n"/>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="27" t="n"/>
-      <c r="F8" s="27" t="n">
+      <c r="B9" s="27" t="n"/>
+      <c r="C9" s="27" t="n"/>
+      <c r="D9" s="27" t="n"/>
+      <c r="E9" s="27" t="n"/>
+      <c r="F9" s="27" t="n">
         <v>0</v>
       </c>
     </row>

--- a/jira_export_2026-09-08.xlsx
+++ b/jira_export_2026-09-08.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>10,730 €</t>
+          <t>10,955 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -767,7 +767,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>7,373 €</t>
+          <t>7,598 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>122 h</t>
+          <t>123 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P100"/>
+  <dimension ref="A1:P101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -949,7 +949,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -1342,37 +1342,37 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35037</t>
+          <t>PDMDEP-35148</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VILLEFRANCHE SUR SAONE ] - mise a jour carto comprise dans leur abonnement annuel </t>
+          <t>[MAIRIE DES PORTES EN RE] - UPSELL PAX</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
+          <t>Mairie de Les Portes En Ré</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">mise a jour carto comprise dans leur abonnement annuel </t>
+          <t>UPSELL PAX</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
@@ -1382,22 +1382,30 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="J9" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L9" s="11" t="inlineStr"/>
-      <c r="M9" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35156</t>
+        </is>
+      </c>
+      <c r="M9" s="11" t="inlineStr">
+        <is>
+          <t>00178841</t>
+        </is>
+      </c>
       <c r="N9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>0</v>
@@ -1406,12 +1414,12 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-35029</t>
+          <t>PDMDEP-35037</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE LEVALLOIS PERRET] - Hébergement Litt Exp test et prod</t>
+          <t xml:space="preserve">[VILLE DE VILLEFRANCHE SUR SAONE ] - mise a jour carto comprise dans leur abonnement annuel </t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
@@ -1421,12 +1429,12 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE LEVALLOIS PERRET</t>
+          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hébergement Litt Exp </t>
+          <t xml:space="preserve">mise a jour carto comprise dans leur abonnement annuel </t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
@@ -1436,7 +1444,7 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H10" s="14" t="inlineStr">
@@ -1453,7 +1461,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="14" t="n">
-        <v>4</v>
+        <v>1.75</v>
       </c>
       <c r="L10" s="14" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -1470,27 +1478,27 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34975</t>
+          <t>PDMDEP-35029</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t>[VILLE DE LEVALLOIS PERRET] - Hébergement Litt Exp test et prod</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>VILLE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t xml:space="preserve">Hébergement Litt Exp </t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -1500,7 +1508,7 @@
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
@@ -1510,29 +1518,21 @@
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="J11" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34979</t>
-        </is>
-      </c>
-      <c r="M11" s="11" t="inlineStr">
-        <is>
-          <t>00178226</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="L11" s="11" t="inlineStr"/>
+      <c r="M11" s="11" t="inlineStr"/>
       <c r="N11" s="12" t="n">
-        <v>1100</v>
-      </c>
-      <c r="O11" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P11" s="12" t="n">
@@ -1542,32 +1542,32 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34819</t>
+          <t>PDMDEP-34975</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>[Ville de Bourges] - Migration GEODP Placier et ODP</t>
+          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Ville de Bourges</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier et ODP</t>
+          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -1577,35 +1577,35 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="J12" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K12" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34825</t>
+          <t>PDMDEP-34979</t>
         </is>
       </c>
       <c r="M12" s="14" t="inlineStr">
         <is>
-          <t>00177218</t>
+          <t>00178226</t>
         </is>
       </c>
       <c r="N12" s="15" t="n">
-        <v>2419</v>
+        <v>1100</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>120.95</v>
+        <v>0</v>
       </c>
       <c r="P12" s="15" t="n">
         <v>0</v>
@@ -1614,27 +1614,27 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34782</t>
+          <t>PDMDEP-34819</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
+          <t>[Ville de Bourges] - Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>Ville de Bourges</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>GEODP PLACIER</t>
+          <t>Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
@@ -1661,52 +1661,52 @@
         <v>2</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34791</t>
+          <t>PDMDEP-34825</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>00177122</t>
+          <t>00177218</t>
         </is>
       </c>
       <c r="N13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="12" t="n">
-        <v>643.95</v>
+        <v>2419</v>
+      </c>
+      <c r="O13" s="16" t="n">
+        <v>120.95</v>
       </c>
       <c r="P13" s="12" t="n">
-        <v>321.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34761</t>
+          <t>PDMDEP-34782</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>GEODP PLACIER</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
@@ -1721,69 +1721,69 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J14" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K14" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34768</t>
+          <t>PDMDEP-34791</t>
         </is>
       </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
-          <t>00177029</t>
+          <t>00177122</t>
         </is>
       </c>
       <c r="N14" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>726.05</v>
+        <v>643.95</v>
       </c>
       <c r="P14" s="15" t="n">
-        <v>0</v>
+        <v>321.98</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34718</t>
+          <t>PDMDEP-34761</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Crédits d'heure (14h)</t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
@@ -1793,49 +1793,49 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="J15" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34722</t>
+          <t>PDMDEP-34768</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>00176875</t>
+          <t>00177029</t>
         </is>
       </c>
       <c r="N15" s="12" t="n">
-        <v>1260</v>
-      </c>
-      <c r="O15" s="16" t="n">
-        <v>728</v>
+        <v>0</v>
+      </c>
+      <c r="O15" s="12" t="n">
+        <v>726.05</v>
       </c>
       <c r="P15" s="12" t="n">
-        <v>264.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34495</t>
+          <t>PDMDEP-34718</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
+          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CLICHY</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
+          <t>Crédits d'heure (14h)</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -1870,64 +1870,64 @@
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="J16" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34499</t>
+          <t>PDMDEP-34722</t>
         </is>
       </c>
       <c r="M16" s="14" t="inlineStr">
         <is>
-          <t>00172678</t>
+          <t>00176875</t>
         </is>
       </c>
       <c r="N16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="15" t="n">
-        <v>43</v>
+        <v>1260</v>
+      </c>
+      <c r="O16" s="16" t="n">
+        <v>728</v>
       </c>
       <c r="P16" s="15" t="n">
-        <v>19.11</v>
+        <v>264.73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34475</t>
+          <t>PDMDEP-34495</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>[Mairie de Pontcharra] - Migration simple placier</t>
+          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Pontcharra</t>
+          <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Migration simple placier</t>
+          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -1937,49 +1937,49 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="J17" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34481</t>
+          <t>PDMDEP-34499</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>00172611</t>
+          <t>00172678</t>
         </is>
       </c>
       <c r="N17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="P17" s="12" t="n">
-        <v>70</v>
+        <v>19.11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34411</t>
+          <t>PDMDEP-34475</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Mairie de Pontcharra] - Migration simple placier</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
@@ -1989,12 +1989,12 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE MAIZIERES LES METZ</t>
+          <t>Mairie de Pontcharra</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Migration simple placier</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -2014,44 +2014,44 @@
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="J18" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K18" s="14" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34420</t>
+          <t>PDMDEP-34481</t>
         </is>
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>00172317</t>
+          <t>00172611</t>
         </is>
       </c>
       <c r="N18" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="P18" s="15" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34411</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>MAIRIE DE MAIZIERES LES METZ</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -2086,29 +2086,29 @@
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="J19" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34420</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00172317</t>
         </is>
       </c>
       <c r="N19" s="12" t="n">
-        <v>769.5</v>
-      </c>
-      <c r="O19" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P19" s="12" t="n">
@@ -2118,27 +2118,27 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34287</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP </t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
@@ -2158,21 +2158,29 @@
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J20" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L20" s="14" t="inlineStr"/>
-      <c r="M20" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34326</t>
+        </is>
+      </c>
+      <c r="M20" s="14" t="inlineStr">
+        <is>
+          <t>00171691</t>
+        </is>
+      </c>
       <c r="N20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="15" t="n">
+        <v>769.5</v>
+      </c>
+      <c r="O20" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P20" s="15" t="n">
@@ -2182,27 +2190,27 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34287</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t xml:space="preserve">Migration GeODP </t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -2212,7 +2220,7 @@
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
@@ -2229,22 +2237,14 @@
         <v>3</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34258</t>
-        </is>
-      </c>
-      <c r="M21" s="11" t="inlineStr">
-        <is>
-          <t>00171361</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L21" s="11" t="inlineStr"/>
+      <c r="M21" s="11" t="inlineStr"/>
       <c r="N21" s="12" t="n">
-        <v>2127.2</v>
-      </c>
-      <c r="O21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P21" s="12" t="n">
@@ -2254,32 +2254,32 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -2289,69 +2289,69 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J22" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N22" s="15" t="n">
-        <v>4536</v>
+        <v>2127.2</v>
       </c>
       <c r="O22" s="16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="P22" s="15" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -2361,49 +2361,49 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J23" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N23" s="12" t="n">
-        <v>525</v>
+        <v>4536</v>
       </c>
       <c r="O23" s="16" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="P23" s="12" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I24" s="14" t="inlineStr">
@@ -2445,52 +2445,52 @@
         <v>3</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N24" s="15" t="n">
-        <v>1662</v>
+        <v>525</v>
       </c>
       <c r="O24" s="16" t="n">
-        <v>277</v>
+        <v>0</v>
       </c>
       <c r="P24" s="15" t="n">
-        <v>277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -2505,49 +2505,49 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J25" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="N25" s="12" t="n">
-        <v>9623.1</v>
+        <v>1662</v>
       </c>
       <c r="O25" s="16" t="n">
-        <v>320.77</v>
+        <v>277</v>
       </c>
       <c r="P25" s="12" t="n">
-        <v>0</v>
+        <v>277</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J26" s="14" t="n">
@@ -2593,19 +2593,19 @@
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N26" s="15" t="n">
-        <v>707</v>
+        <v>9623.1</v>
       </c>
       <c r="O26" s="16" t="n">
-        <v>0</v>
+        <v>320.77</v>
       </c>
       <c r="P26" s="15" t="n">
         <v>0</v>
@@ -2614,12 +2614,12 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -2649,12 +2649,12 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="J27" s="11" t="n">
@@ -2665,16 +2665,16 @@
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>300</v>
+        <v>707</v>
       </c>
       <c r="O27" s="16" t="n">
         <v>0</v>
@@ -2686,27 +2686,27 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
@@ -2721,12 +2721,12 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J28" s="14" t="n">
@@ -2737,16 +2737,16 @@
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N28" s="15" t="n">
-        <v>510</v>
+        <v>300</v>
       </c>
       <c r="O28" s="16" t="n">
         <v>0</v>
@@ -2758,32 +2758,32 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
@@ -2793,64 +2793,64 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>242.9</v>
-      </c>
-      <c r="O29" s="12" t="n">
-        <v>248.58</v>
+        <v>510</v>
+      </c>
+      <c r="O29" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P29" s="12" t="n">
-        <v>124.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
@@ -2877,37 +2877,37 @@
         <v>3</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N30" s="15" t="n">
-        <v>220</v>
-      </c>
-      <c r="O30" s="16" t="n">
-        <v>0</v>
+        <v>242.9</v>
+      </c>
+      <c r="O30" s="15" t="n">
+        <v>248.58</v>
       </c>
       <c r="P30" s="15" t="n">
-        <v>0</v>
+        <v>124.29</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -2942,44 +2942,44 @@
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="12" t="n">
-        <v>65.73</v>
+        <v>220</v>
+      </c>
+      <c r="O31" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P31" s="12" t="n">
-        <v>52.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
@@ -3021,52 +3021,52 @@
         <v>3</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N32" s="15" t="n">
-        <v>1890</v>
-      </c>
-      <c r="O32" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O32" s="15" t="n">
+        <v>65.73</v>
       </c>
       <c r="P32" s="15" t="n">
-        <v>0</v>
+        <v>52.58</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commande modélisation supplémentaire </t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -3086,44 +3086,44 @@
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="12" t="n">
-        <v>266.2</v>
+        <v>1890</v>
+      </c>
+      <c r="O33" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P33" s="12" t="n">
-        <v>96.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
@@ -3158,59 +3158,59 @@
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J34" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K34" s="14" t="n">
-        <v>1.5</v>
+        <v>2.75</v>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N34" s="15" t="n">
-        <v>920</v>
-      </c>
-      <c r="O34" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O34" s="15" t="n">
+        <v>266.2</v>
       </c>
       <c r="P34" s="15" t="n">
-        <v>0</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33699</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>[CD 35)] - Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3230,64 +3230,64 @@
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33703</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00169363</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="12" t="n">
-        <v>540</v>
+        <v>920</v>
+      </c>
+      <c r="O35" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P35" s="12" t="n">
-        <v>720</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33610</t>
+          <t>PDMDEP-33699</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
+          <t>[CD 35)] - Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MORLAIX</t>
+          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+          <t>Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
@@ -3297,64 +3297,64 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="J36" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K36" s="14" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33616</t>
+          <t>PDMDEP-33703</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>00169015</t>
+          <t>00169363</t>
         </is>
       </c>
       <c r="N36" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O36" s="15" t="n">
-        <v>505</v>
+        <v>540</v>
       </c>
       <c r="P36" s="15" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33610</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>COMMUNE DE MORLAIX</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
@@ -3381,23 +3381,23 @@
         <v>3</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33616</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169015</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>0</v>
+        <v>505</v>
       </c>
       <c r="P37" s="12" t="n">
         <v>0</v>
@@ -3406,12 +3406,12 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33500</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mairie de Carcès </t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
@@ -3441,69 +3441,69 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J38" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K38" s="14" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33509</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>00168117</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N38" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O38" s="15" t="n">
-        <v>691.9</v>
+        <v>0</v>
       </c>
       <c r="P38" s="15" t="n">
-        <v>461.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33500</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t xml:space="preserve">Mairie de Carcès </t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
@@ -3513,69 +3513,69 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33509</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00168117</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>171.4</v>
-      </c>
-      <c r="O39" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O39" s="12" t="n">
+        <v>691.9</v>
       </c>
       <c r="P39" s="12" t="n">
-        <v>0</v>
+        <v>461.27</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J40" s="14" t="n">
@@ -3601,19 +3601,19 @@
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="15" t="n">
-        <v>3339.2</v>
+        <v>171.4</v>
+      </c>
+      <c r="O40" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P40" s="15" t="n">
         <v>0</v>
@@ -3622,27 +3622,27 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
@@ -3673,19 +3673,19 @@
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>344</v>
-      </c>
-      <c r="O41" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O41" s="12" t="n">
+        <v>3339.2</v>
       </c>
       <c r="P41" s="12" t="n">
         <v>0</v>
@@ -3694,27 +3694,27 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J42" s="14" t="n">
@@ -3745,16 +3745,16 @@
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N42" s="15" t="n">
-        <v>500</v>
+        <v>344</v>
       </c>
       <c r="O42" s="16" t="n">
         <v>0</v>
@@ -3766,27 +3766,27 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
@@ -3817,16 +3817,16 @@
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>149</v>
+        <v>500</v>
       </c>
       <c r="O43" s="16" t="n">
         <v>0</v>
@@ -3838,32 +3838,32 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -3873,38 +3873,38 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J44" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
-        <v>625</v>
+        <v>149</v>
       </c>
       <c r="O44" s="16" t="n">
-        <v>337.5</v>
+        <v>0</v>
       </c>
       <c r="P44" s="15" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -3961,53 +3961,53 @@
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="12" t="n">
-        <v>16</v>
+        <v>625</v>
+      </c>
+      <c r="O45" s="16" t="n">
+        <v>337.5</v>
       </c>
       <c r="P45" s="12" t="n">
-        <v>25.6</v>
+        <v>540</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -4017,49 +4017,49 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J46" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K46" s="14" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>910</v>
-      </c>
-      <c r="O46" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O46" s="15" t="n">
+        <v>16</v>
       </c>
       <c r="P46" s="15" t="n">
-        <v>0</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -4094,27 +4094,27 @@
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>1207</v>
+        <v>910</v>
       </c>
       <c r="O47" s="16" t="n">
         <v>0</v>
@@ -4126,32 +4126,32 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -4161,32 +4161,32 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K48" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>500</v>
+        <v>1207</v>
       </c>
       <c r="O48" s="16" t="n">
         <v>0</v>
@@ -4198,27 +4198,27 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -4238,29 +4238,29 @@
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="12" t="n">
+        <v>500</v>
+      </c>
+      <c r="O49" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P49" s="12" t="n">
@@ -4270,12 +4270,12 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
@@ -4310,29 +4310,29 @@
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K50" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O50" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P50" s="15" t="n">
@@ -4342,32 +4342,32 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
@@ -4377,32 +4377,32 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K51" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>2335</v>
+        <v>142.1</v>
       </c>
       <c r="O51" s="16" t="n">
         <v>0</v>
@@ -4414,32 +4414,32 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -4449,34 +4449,34 @@
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K52" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="15" t="n">
+        <v>2335</v>
+      </c>
+      <c r="O52" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P52" s="15" t="n">
@@ -4486,32 +4486,32 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32366</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>Commune de Pleneuf Val André</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -4521,28 +4521,28 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32372</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00161594</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
@@ -4558,12 +4558,12 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32366</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>Commune de Pleneuf Val André</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
@@ -4598,29 +4598,29 @@
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K54" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32372</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161594</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>450</v>
-      </c>
-      <c r="O54" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P54" s="15" t="n">
@@ -4630,32 +4630,32 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -4665,69 +4665,69 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O55" s="16" t="n">
-        <v>136.5</v>
+        <v>0</v>
       </c>
       <c r="P55" s="12" t="n">
-        <v>68.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -4737,49 +4737,49 @@
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K56" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>590.15</v>
+        <v>910</v>
       </c>
       <c r="O56" s="16" t="n">
-        <v>0</v>
+        <v>136.5</v>
       </c>
       <c r="P56" s="15" t="n">
-        <v>0</v>
+        <v>68.25</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
@@ -4825,16 +4825,16 @@
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>285</v>
+        <v>590.15</v>
       </c>
       <c r="O57" s="16" t="n">
         <v>0</v>
@@ -4846,32 +4846,32 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -4886,27 +4886,27 @@
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
-        <v>1325</v>
+        <v>285</v>
       </c>
       <c r="O58" s="16" t="n">
         <v>0</v>
@@ -4918,12 +4918,12 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
@@ -4933,12 +4933,12 @@
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -4958,27 +4958,27 @@
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>120</v>
+        <v>1325</v>
       </c>
       <c r="O59" s="16" t="n">
         <v>0</v>
@@ -4990,32 +4990,32 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
@@ -5041,16 +5041,16 @@
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>588</v>
+        <v>120</v>
       </c>
       <c r="O60" s="16" t="n">
         <v>0</v>
@@ -5062,27 +5062,27 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -5097,32 +5097,32 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K61" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>203.5</v>
+        <v>588</v>
       </c>
       <c r="O61" s="16" t="n">
         <v>0</v>
@@ -5134,12 +5134,12 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
@@ -5149,12 +5149,12 @@
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J62" s="14" t="n">
@@ -5185,16 +5185,16 @@
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
-        <v>300</v>
+        <v>203.5</v>
       </c>
       <c r="O62" s="16" t="n">
         <v>0</v>
@@ -5206,32 +5206,32 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
@@ -5241,12 +5241,12 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
@@ -5257,16 +5257,16 @@
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="O63" s="16" t="n">
         <v>0</v>
@@ -5278,32 +5278,32 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J64" s="14" t="n">
@@ -5329,16 +5329,16 @@
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N64" s="15" t="n">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="O64" s="16" t="n">
         <v>0</v>
@@ -5350,12 +5350,12 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
@@ -5401,19 +5401,19 @@
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" s="12" t="n">
-        <v>281</v>
+        <v>210</v>
+      </c>
+      <c r="O65" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P65" s="12" t="n">
         <v>0</v>
@@ -5422,12 +5422,12 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
@@ -5437,12 +5437,12 @@
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
@@ -5473,19 +5473,19 @@
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
-        <v>130</v>
-      </c>
-      <c r="O66" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O66" s="15" t="n">
+        <v>281</v>
       </c>
       <c r="P66" s="15" t="n">
         <v>0</v>
@@ -5494,12 +5494,12 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
@@ -5545,16 +5545,16 @@
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O67" s="16" t="n">
         <v>0</v>
@@ -5566,12 +5566,12 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
@@ -5606,27 +5606,27 @@
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K68" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O68" s="16" t="n">
         <v>0</v>
@@ -5638,32 +5638,32 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
@@ -5673,32 +5673,32 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
         <v>8</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>690</v>
+        <v>140</v>
       </c>
       <c r="O69" s="16" t="n">
         <v>0</v>
@@ -5710,27 +5710,27 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
@@ -5750,27 +5750,27 @@
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J70" s="14" t="n">
         <v>8</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>187.5</v>
+        <v>690</v>
       </c>
       <c r="O70" s="16" t="n">
         <v>0</v>
@@ -5833,16 +5833,16 @@
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O71" s="16" t="n">
         <v>0</v>
@@ -5854,32 +5854,32 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
@@ -5889,35 +5889,35 @@
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K72" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" s="15" t="n">
-        <v>362.5</v>
+        <v>787.5</v>
+      </c>
+      <c r="O72" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P72" s="15" t="n">
         <v>0</v>
@@ -5926,30 +5926,32 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E73" s="11" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
@@ -5959,35 +5961,35 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O73" s="12" t="n">
-        <v>0</v>
+        <v>362.5</v>
       </c>
       <c r="P73" s="12" t="n">
         <v>0</v>
@@ -5996,12 +5998,12 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
@@ -6011,13 +6013,11 @@
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E74" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E74" s="14" t="n">
+        <v/>
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
@@ -6036,23 +6036,23 @@
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K74" s="14" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
@@ -6119,12 +6119,12 @@
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
@@ -6191,12 +6191,12 @@
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
@@ -6335,18 +6335,18 @@
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O78" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P78" s="15" t="n">
@@ -6356,12 +6356,12 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
@@ -6371,11 +6371,13 @@
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E79" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
@@ -6389,34 +6391,34 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" s="12" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O79" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P79" s="12" t="n">
@@ -6426,12 +6428,12 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
@@ -6441,34 +6443,48 @@
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>CD74</t>
-        </is>
-      </c>
-      <c r="E80" s="14" t="inlineStr">
-        <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F80" s="14" t="inlineStr"/>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
+        </is>
+      </c>
+      <c r="E80" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F80" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G80" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H80" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H80" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K80" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L80" s="14" t="inlineStr"/>
-      <c r="M80" s="14" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L80" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27642</t>
+        </is>
+      </c>
+      <c r="M80" s="14" t="inlineStr">
+        <is>
+          <t>00143935</t>
+        </is>
+      </c>
       <c r="N80" s="15" t="n">
         <v>0</v>
       </c>
@@ -6482,12 +6498,12 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
@@ -6497,48 +6513,34 @@
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
-        </is>
-      </c>
-      <c r="E81" s="11" t="n">
-        <v/>
-      </c>
-      <c r="F81" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F81" s="11" t="inlineStr"/>
       <c r="G81" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H81" s="11" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H81" s="11" t="inlineStr"/>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L81" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-26814</t>
-        </is>
-      </c>
-      <c r="M81" s="11" t="inlineStr">
-        <is>
-          <t>00142941</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L81" s="11" t="inlineStr"/>
+      <c r="M81" s="11" t="inlineStr"/>
       <c r="N81" s="12" t="n">
         <v>0</v>
       </c>
@@ -6552,12 +6554,12 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
@@ -6567,7 +6569,7 @@
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E82" s="14" t="n">
@@ -6585,34 +6587,34 @@
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O82" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P82" s="15" t="n">
@@ -6622,12 +6624,12 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
@@ -6637,7 +6639,7 @@
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E83" s="11" t="n">
@@ -6660,29 +6662,29 @@
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" s="12" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O83" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P83" s="12" t="n">
@@ -6692,12 +6694,12 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23750</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>MEL - LITTERALIS x AXION</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
@@ -6707,13 +6709,11 @@
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
-        </is>
-      </c>
-      <c r="E84" s="14" t="inlineStr">
-        <is>
-          <t>AXION</t>
-        </is>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+        </is>
+      </c>
+      <c r="E84" s="14" t="n">
+        <v/>
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
@@ -6722,33 +6722,33 @@
       </c>
       <c r="G84" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>08/08/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J84" s="14" t="n">
         <v>13</v>
       </c>
       <c r="K84" s="14" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27033</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>497304</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
@@ -6764,26 +6764,28 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-23750</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>MEL - LITTERALIS x AXION</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
-        </is>
-      </c>
-      <c r="E85" s="11" t="n">
-        <v/>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>AXION</t>
+        </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
@@ -6792,7 +6794,7 @@
       </c>
       <c r="G85" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H85" s="11" t="inlineStr">
@@ -6802,29 +6804,29 @@
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>08/08/2025</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27033</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>497304</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>401</v>
-      </c>
-      <c r="O85" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P85" s="12" t="n">
@@ -6834,12 +6836,12 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
@@ -6849,7 +6851,7 @@
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E86" s="14" t="n">
@@ -6867,34 +6869,34 @@
       </c>
       <c r="H86" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J86" s="14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K86" s="14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" s="15" t="n">
+        <v>401</v>
+      </c>
+      <c r="O86" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P86" s="15" t="n">
@@ -6904,22 +6906,22 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E87" s="11" t="n">
@@ -6937,28 +6939,28 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
         <v>17</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>0.5</v>
+        <v>3.25</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
@@ -6974,22 +6976,22 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E88" s="14" t="n">
@@ -7012,29 +7014,29 @@
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
         <v>17</v>
       </c>
       <c r="K88" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
-        <v>230</v>
-      </c>
-      <c r="O88" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P88" s="15" t="n">
@@ -7044,22 +7046,22 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E89" s="11" t="n">
@@ -7077,34 +7079,34 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28215</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>458306</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="O89" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P89" s="12" t="n">
@@ -7163,12 +7165,12 @@
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28214</t>
+          <t>PDMDEP-28215</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
         <is>
-          <t>458286</t>
+          <t>458306</t>
         </is>
       </c>
       <c r="N90" s="15" t="n">
@@ -7184,12 +7186,12 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
@@ -7199,7 +7201,7 @@
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E91" s="11" t="n">
@@ -7212,27 +7214,35 @@
       </c>
       <c r="G91" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L91" s="11" t="inlineStr"/>
-      <c r="M91" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L91" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28214</t>
+        </is>
+      </c>
+      <c r="M91" s="11" t="inlineStr">
+        <is>
+          <t>458286</t>
+        </is>
+      </c>
       <c r="N91" s="12" t="n">
         <v>0</v>
       </c>
@@ -7246,22 +7256,22 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E92" s="14" t="n">
@@ -7279,7 +7289,7 @@
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I92" s="14" t="inlineStr">
@@ -7291,7 +7301,7 @@
         <v>21</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="L92" s="14" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -7308,22 +7318,22 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E93" s="11" t="n">
@@ -7331,44 +7341,36 @@
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
         <v>21</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M93" s="11" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>3.08</v>
+      </c>
+      <c r="L93" s="11" t="inlineStr"/>
+      <c r="M93" s="11" t="inlineStr"/>
       <c r="N93" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O93" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P93" s="12" t="n">
@@ -7378,22 +7380,22 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E94" s="14" t="n">
@@ -7401,7 +7403,7 @@
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G94" s="14" t="inlineStr">
@@ -7411,12 +7413,12 @@
       </c>
       <c r="H94" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
@@ -7427,16 +7429,16 @@
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
-        <v>557.145</v>
+        <v>240</v>
       </c>
       <c r="O94" s="16" t="n">
         <v>0</v>
@@ -7448,22 +7450,22 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E95" s="11" t="n">
@@ -7476,31 +7478,39 @@
       </c>
       <c r="G95" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L95" s="11" t="inlineStr"/>
-      <c r="M95" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L95" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M95" s="11" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N95" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" s="12" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O95" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P95" s="12" t="n">
@@ -7510,22 +7520,22 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13128</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E96" s="14" t="n">
@@ -7538,35 +7548,27 @@
       </c>
       <c r="G96" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K96" s="14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L96" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M96" s="14" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>1.75</v>
+      </c>
+      <c r="L96" s="14" t="inlineStr"/>
+      <c r="M96" s="14" t="inlineStr"/>
       <c r="N96" s="15" t="n">
         <v>0</v>
       </c>
@@ -7580,22 +7582,22 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E97" s="11" t="n">
@@ -7608,23 +7610,35 @@
       </c>
       <c r="G97" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H97" s="11" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H97" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
         <v>36</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L97" s="11" t="inlineStr"/>
-      <c r="M97" s="11" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L97" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M97" s="11" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N97" s="12" t="n">
         <v>0</v>
       </c>
@@ -7638,24 +7652,26 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C98" s="14" t="inlineStr"/>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C98" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E98" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CD 56 MORBIHAN</t>
+        </is>
+      </c>
+      <c r="E98" s="14" t="n">
+        <v/>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
@@ -7667,21 +7683,17 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H98" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H98" s="14" t="inlineStr"/>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
         <v>36</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>2.75</v>
+        <v>0.5</v>
       </c>
       <c r="L98" s="14" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -7698,89 +7710,149 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr"/>
       <c r="D99" s="11" t="inlineStr">
         <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G99" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H99" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J99" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="K99" s="11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L99" s="11" t="inlineStr"/>
+      <c r="M99" s="11" t="inlineStr"/>
+      <c r="N99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="13" t="inlineStr">
+        <is>
+          <t>PSC-1270</t>
+        </is>
+      </c>
+      <c r="B100" s="14" t="inlineStr">
+        <is>
           <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
-      <c r="E99" s="11" t="inlineStr"/>
-      <c r="F99" s="11" t="inlineStr">
+      <c r="C100" s="14" t="inlineStr"/>
+      <c r="D100" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="E100" s="14" t="inlineStr"/>
+      <c r="F100" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G99" s="11" t="inlineStr">
+      <c r="G100" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H99" s="11" t="inlineStr"/>
-      <c r="I99" s="11" t="inlineStr">
+      <c r="H100" s="14" t="inlineStr"/>
+      <c r="I100" s="14" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="J99" s="11" t="n">
+      <c r="J100" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="K99" s="11" t="n">
+      <c r="K100" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="L99" s="11" t="inlineStr">
+      <c r="L100" s="14" t="inlineStr">
         <is>
           <t>PDMDEP-33362</t>
         </is>
       </c>
-      <c r="M99" s="11" t="inlineStr">
+      <c r="M100" s="14" t="inlineStr">
         <is>
           <t>00167140</t>
         </is>
       </c>
-      <c r="N99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="17" t="inlineStr">
+      <c r="N100" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B100" s="17" t="inlineStr"/>
-      <c r="C100" s="17" t="inlineStr"/>
-      <c r="D100" s="17" t="inlineStr"/>
-      <c r="E100" s="17" t="inlineStr"/>
-      <c r="F100" s="17" t="inlineStr"/>
-      <c r="G100" s="17" t="inlineStr"/>
-      <c r="H100" s="17" t="inlineStr"/>
-      <c r="I100" s="17" t="inlineStr"/>
-      <c r="J100" s="17" t="inlineStr"/>
-      <c r="K100" s="17" t="inlineStr"/>
-      <c r="L100" s="17" t="inlineStr"/>
-      <c r="M100" s="17" t="inlineStr"/>
-      <c r="N100" s="18" t="n">
+      <c r="B101" s="17" t="inlineStr"/>
+      <c r="C101" s="17" t="inlineStr"/>
+      <c r="D101" s="17" t="inlineStr"/>
+      <c r="E101" s="17" t="inlineStr"/>
+      <c r="F101" s="17" t="inlineStr"/>
+      <c r="G101" s="17" t="inlineStr"/>
+      <c r="H101" s="17" t="inlineStr"/>
+      <c r="I101" s="17" t="inlineStr"/>
+      <c r="J101" s="17" t="inlineStr"/>
+      <c r="K101" s="17" t="inlineStr"/>
+      <c r="L101" s="17" t="inlineStr"/>
+      <c r="M101" s="17" t="inlineStr"/>
+      <c r="N101" s="18" t="n">
         <v>47526.995</v>
       </c>
-      <c r="O100" s="18" t="n">
-        <v>10729.55</v>
-      </c>
-      <c r="P100" s="18" t="n">
-        <v>150.44</v>
+      <c r="O101" s="18" t="n">
+        <v>10954.55</v>
+      </c>
+      <c r="P101" s="18" t="n">
+        <v>150.43</v>
       </c>
     </row>
   </sheetData>
@@ -7881,6 +7953,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId96"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8641,13 +8714,13 @@
         <v>38.25</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>10.08</v>
+        <v>11.58</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>5.75</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>54.08</v>
+        <v>55.58</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>7.17</v>
@@ -8657,7 +8730,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.5%</t>
         </is>
       </c>
     </row>
@@ -8784,10 +8857,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>396735</v>
+        <v>396510</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>166191</v>
+        <v>165966</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>230544</v>
@@ -8834,10 +8907,10 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>231380</v>
+        <v>231155</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>103215</v>
+        <v>102990</v>
       </c>
       <c r="D7" s="26" t="n">
         <v>128164</v>

--- a/jira_export_2026-09-08.xlsx
+++ b/jira_export_2026-09-08.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>123 h</t>
+          <t>134 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>273</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P101"/>
+  <dimension ref="A1:P109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -5757,7 +5757,7 @@
         <v>8</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
@@ -5829,22 +5829,22 @@
         <v>8</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="O71" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P71" s="12" t="n">
@@ -5901,20 +5901,20 @@
         <v>8</v>
       </c>
       <c r="K72" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O72" s="16" t="n">
         <v>0</v>
@@ -5926,32 +5926,32 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
@@ -5961,35 +5961,35 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" s="12" t="n">
-        <v>362.5</v>
+        <v>787.5</v>
+      </c>
+      <c r="O73" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P73" s="12" t="n">
         <v>0</v>
@@ -5998,30 +5998,32 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E74" s="14" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E74" s="14" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -6031,35 +6033,35 @@
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K74" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O74" s="15" t="n">
-        <v>0</v>
+        <v>362.5</v>
       </c>
       <c r="P74" s="15" t="n">
         <v>0</v>
@@ -6068,12 +6070,12 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
@@ -6083,13 +6085,11 @@
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E75" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="n">
+        <v/>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
@@ -6108,23 +6108,23 @@
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.9</v>
+        <v>2.75</v>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
@@ -6187,16 +6187,16 @@
         <v>10</v>
       </c>
       <c r="K76" s="14" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
@@ -6259,16 +6259,16 @@
         <v>10</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
@@ -6331,16 +6331,16 @@
         <v>10</v>
       </c>
       <c r="K78" s="14" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
@@ -6403,22 +6403,22 @@
         <v>10</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O79" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P79" s="12" t="n">
@@ -6428,12 +6428,12 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
@@ -6443,11 +6443,13 @@
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E80" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E80" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
@@ -6461,34 +6463,34 @@
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K80" s="14" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N80" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" s="15" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O80" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P80" s="15" t="n">
@@ -6498,12 +6500,12 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
@@ -6513,34 +6515,48 @@
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>CD74</t>
-        </is>
-      </c>
-      <c r="E81" s="11" t="inlineStr">
-        <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F81" s="11" t="inlineStr"/>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F81" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G81" s="11" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H81" s="11" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H81" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L81" s="11" t="inlineStr"/>
-      <c r="M81" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L81" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27642</t>
+        </is>
+      </c>
+      <c r="M81" s="11" t="inlineStr">
+        <is>
+          <t>00143935</t>
+        </is>
+      </c>
       <c r="N81" s="12" t="n">
         <v>0</v>
       </c>
@@ -6554,12 +6570,12 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
@@ -6569,48 +6585,34 @@
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
-        </is>
-      </c>
-      <c r="E82" s="14" t="n">
-        <v/>
-      </c>
-      <c r="F82" s="14" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E82" s="14" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F82" s="14" t="inlineStr"/>
       <c r="G82" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H82" s="14" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H82" s="14" t="inlineStr"/>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L82" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-26814</t>
-        </is>
-      </c>
-      <c r="M82" s="14" t="inlineStr">
-        <is>
-          <t>00142941</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L82" s="14" t="inlineStr"/>
+      <c r="M82" s="14" t="inlineStr"/>
       <c r="N82" s="15" t="n">
         <v>0</v>
       </c>
@@ -6624,12 +6626,12 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
@@ -6639,7 +6641,7 @@
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E83" s="11" t="n">
@@ -6657,34 +6659,34 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O83" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P83" s="12" t="n">
@@ -6694,12 +6696,12 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
@@ -6709,7 +6711,7 @@
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E84" s="14" t="n">
@@ -6732,29 +6734,29 @@
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J84" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K84" s="14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" s="15" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O84" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P84" s="15" t="n">
@@ -6764,12 +6766,12 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23750</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>MEL - LITTERALIS x AXION</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
@@ -6779,13 +6781,11 @@
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
-        </is>
-      </c>
-      <c r="E85" s="11" t="inlineStr">
-        <is>
-          <t>AXION</t>
-        </is>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="n">
+        <v/>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
@@ -6794,33 +6794,33 @@
       </c>
       <c r="G85" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>08/08/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
         <v>13</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27033</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>497304</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
@@ -6836,26 +6836,28 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-23750</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>MEL - LITTERALIS x AXION</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
-        </is>
-      </c>
-      <c r="E86" s="14" t="n">
-        <v/>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
+        </is>
+      </c>
+      <c r="E86" s="14" t="inlineStr">
+        <is>
+          <t>AXION</t>
+        </is>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
@@ -6864,7 +6866,7 @@
       </c>
       <c r="G86" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H86" s="14" t="inlineStr">
@@ -6874,29 +6876,29 @@
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>08/08/2025</t>
         </is>
       </c>
       <c r="J86" s="14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K86" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27033</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>497304</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
-        <v>401</v>
-      </c>
-      <c r="O86" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P86" s="15" t="n">
@@ -6906,22 +6908,22 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E87" s="11" t="n">
@@ -6944,23 +6946,23 @@
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>3.25</v>
+        <v>0.06</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
@@ -6976,12 +6978,12 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
@@ -6991,7 +6993,7 @@
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E88" s="14" t="n">
@@ -7009,28 +7011,28 @@
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K88" s="14" t="n">
-        <v>0.5</v>
+        <v>0.06</v>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
@@ -7046,22 +7048,22 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E89" s="11" t="n">
@@ -7079,34 +7081,34 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
-        <v>230</v>
-      </c>
-      <c r="O89" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P89" s="12" t="n">
@@ -7116,12 +7118,12 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
@@ -7131,7 +7133,7 @@
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E90" s="14" t="n">
@@ -7154,23 +7156,23 @@
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J90" s="14" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K90" s="14" t="n">
-        <v>0.5</v>
+        <v>0.06</v>
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28215</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
         <is>
-          <t>458306</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N90" s="15" t="n">
@@ -7186,12 +7188,12 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-22126</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>[MEL Lille] - LITTERALIS - 3 jours de modélisation / param / accomp (21h)</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
@@ -7201,7 +7203,7 @@
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>Métropole Européenne de Lille</t>
         </is>
       </c>
       <c r="E91" s="11" t="n">
@@ -7219,28 +7221,28 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28214</t>
+          <t>PDMDEP-27368</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>458286</t>
+          <t>484163</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
@@ -7256,22 +7258,22 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E92" s="14" t="n">
@@ -7284,7 +7286,7 @@
       </c>
       <c r="G92" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H92" s="14" t="inlineStr">
@@ -7294,21 +7296,29 @@
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J92" s="14" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L92" s="14" t="inlineStr"/>
-      <c r="M92" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L92" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27373</t>
+        </is>
+      </c>
+      <c r="M92" s="14" t="inlineStr">
+        <is>
+          <t>466234</t>
+        </is>
+      </c>
       <c r="N92" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" s="15" t="n">
+        <v>401</v>
+      </c>
+      <c r="O92" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="15" t="n">
@@ -7318,12 +7328,12 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
@@ -7333,7 +7343,7 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E93" s="11" t="n">
@@ -7346,7 +7356,7 @@
       </c>
       <c r="G93" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H93" s="11" t="inlineStr">
@@ -7356,17 +7366,25 @@
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="L93" s="11" t="inlineStr"/>
-      <c r="M93" s="11" t="inlineStr"/>
+        <v>3.25</v>
+      </c>
+      <c r="L93" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28036</t>
+        </is>
+      </c>
+      <c r="M93" s="11" t="inlineStr">
+        <is>
+          <t>483799</t>
+        </is>
+      </c>
       <c r="N93" s="12" t="n">
         <v>0</v>
       </c>
@@ -7380,22 +7398,22 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E94" s="14" t="n">
@@ -7403,7 +7421,7 @@
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G94" s="14" t="inlineStr">
@@ -7413,34 +7431,34 @@
       </c>
       <c r="H94" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K94" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="O94" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P94" s="15" t="n">
@@ -7450,12 +7468,12 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
@@ -7465,7 +7483,7 @@
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E95" s="11" t="n">
@@ -7488,27 +7506,27 @@
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K95" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
-        <v>557.145</v>
+        <v>230</v>
       </c>
       <c r="O95" s="16" t="n">
         <v>0</v>
@@ -7520,22 +7538,22 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E96" s="14" t="n">
@@ -7548,27 +7566,35 @@
       </c>
       <c r="G96" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="K96" s="14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L96" s="14" t="inlineStr"/>
-      <c r="M96" s="14" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L96" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27568</t>
+        </is>
+      </c>
+      <c r="M96" s="14" t="inlineStr">
+        <is>
+          <t>471958</t>
+        </is>
+      </c>
       <c r="N96" s="15" t="n">
         <v>0</v>
       </c>
@@ -7582,22 +7608,22 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E97" s="11" t="n">
@@ -7615,28 +7641,28 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27990</t>
+          <t>PDMDEP-28215</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>406296</t>
+          <t>458306</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
@@ -7652,12 +7678,12 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
@@ -7667,7 +7693,7 @@
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E98" s="14" t="n">
@@ -7680,23 +7706,35 @@
       </c>
       <c r="G98" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H98" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H98" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="K98" s="14" t="n">
         <v>0.5</v>
       </c>
-      <c r="L98" s="14" t="inlineStr"/>
-      <c r="M98" s="14" t="inlineStr"/>
+      <c r="L98" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28214</t>
+        </is>
+      </c>
+      <c r="M98" s="14" t="inlineStr">
+        <is>
+          <t>458286</t>
+        </is>
+      </c>
       <c r="N98" s="15" t="n">
         <v>0</v>
       </c>
@@ -7710,24 +7748,26 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C99" s="11" t="inlineStr"/>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E99" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CD 74 - HAUTE SAVOIE</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="n">
+        <v/>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
@@ -7741,19 +7781,19 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="L99" s="11" t="inlineStr"/>
       <c r="M99" s="11" t="inlineStr"/>
@@ -7770,89 +7810,603 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
+          <t>PDMDEP-18240</t>
+        </is>
+      </c>
+      <c r="B100" s="14" t="inlineStr">
+        <is>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+        </is>
+      </c>
+      <c r="C100" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D100" s="14" t="inlineStr">
+        <is>
+          <t>Biarritz</t>
+        </is>
+      </c>
+      <c r="E100" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F100" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G100" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H100" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I100" s="14" t="inlineStr">
+        <is>
+          <t>20/12/2024</t>
+        </is>
+      </c>
+      <c r="J100" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="K100" s="14" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="L100" s="14" t="inlineStr"/>
+      <c r="M100" s="14" t="inlineStr"/>
+      <c r="N100" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-18115</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>BISCHWILLER</t>
+        </is>
+      </c>
+      <c r="E101" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F101" s="11" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G101" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H101" s="11" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="I101" s="11" t="inlineStr">
+        <is>
+          <t>17/12/2024</t>
+        </is>
+      </c>
+      <c r="J101" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="K101" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M101" s="11" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
+      <c r="N101" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O101" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-18037</t>
+        </is>
+      </c>
+      <c r="B102" s="14" t="inlineStr">
+        <is>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+        </is>
+      </c>
+      <c r="C102" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D102" s="14" t="inlineStr">
+        <is>
+          <t>LE PERREUX SUR MARNE</t>
+        </is>
+      </c>
+      <c r="E102" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F102" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G102" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H102" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I102" s="14" t="inlineStr">
+        <is>
+          <t>12/12/2024</t>
+        </is>
+      </c>
+      <c r="J102" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="K102" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M102" s="14" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
+      <c r="N102" s="15" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O102" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-14118</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>Suresnes</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F103" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G103" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H103" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I103" s="11" t="inlineStr">
+        <is>
+          <t>01/02/2024</t>
+        </is>
+      </c>
+      <c r="J103" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="K103" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L103" s="11" t="inlineStr"/>
+      <c r="M103" s="11" t="inlineStr"/>
+      <c r="N103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-13128</t>
+        </is>
+      </c>
+      <c r="B104" s="14" t="inlineStr">
+        <is>
+          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+        </is>
+      </c>
+      <c r="C104" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D104" s="14" t="inlineStr">
+        <is>
+          <t>Valenciennes</t>
+        </is>
+      </c>
+      <c r="E104" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F104" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G104" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H104" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I104" s="14" t="inlineStr">
+        <is>
+          <t>30/10/2023</t>
+        </is>
+      </c>
+      <c r="J104" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="K104" s="14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="L104" s="14" t="inlineStr"/>
+      <c r="M104" s="14" t="inlineStr"/>
+      <c r="N104" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-12747</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>[FOUGERES] ARPEGE</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>FOUGERES</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G105" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H105" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I105" s="11" t="inlineStr">
+        <is>
+          <t>26/09/2023</t>
+        </is>
+      </c>
+      <c r="J105" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="K105" s="11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L105" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M105" s="11" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
+      <c r="N105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-12708</t>
+        </is>
+      </c>
+      <c r="B106" s="14" t="inlineStr">
+        <is>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C106" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D106" s="14" t="inlineStr">
+        <is>
+          <t>CD 56 MORBIHAN</t>
+        </is>
+      </c>
+      <c r="E106" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F106" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G106" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H106" s="14" t="inlineStr"/>
+      <c r="I106" s="14" t="inlineStr">
+        <is>
+          <t>22/09/2023</t>
+        </is>
+      </c>
+      <c r="J106" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="K106" s="14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L106" s="14" t="inlineStr"/>
+      <c r="M106" s="14" t="inlineStr"/>
+      <c r="N106" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-11477</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr"/>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F107" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G107" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H107" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I107" s="11" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J107" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="K107" s="11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L107" s="11" t="inlineStr"/>
+      <c r="M107" s="11" t="inlineStr"/>
+      <c r="N107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="13" t="inlineStr">
+        <is>
           <t>PSC-1270</t>
         </is>
       </c>
-      <c r="B100" s="14" t="inlineStr">
+      <c r="B108" s="14" t="inlineStr">
         <is>
           <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
-      <c r="C100" s="14" t="inlineStr"/>
-      <c r="D100" s="14" t="inlineStr">
+      <c r="C108" s="14" t="inlineStr"/>
+      <c r="D108" s="14" t="inlineStr">
         <is>
           <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
-      <c r="E100" s="14" t="inlineStr"/>
-      <c r="F100" s="14" t="inlineStr">
+      <c r="E108" s="14" t="inlineStr"/>
+      <c r="F108" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G100" s="14" t="inlineStr">
+      <c r="G108" s="14" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="H100" s="14" t="inlineStr"/>
-      <c r="I100" s="14" t="inlineStr">
+      <c r="H108" s="14" t="inlineStr"/>
+      <c r="I108" s="14" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="J100" s="14" t="n">
+      <c r="J108" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="K100" s="14" t="n">
+      <c r="K108" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="L100" s="14" t="inlineStr">
+      <c r="L108" s="14" t="inlineStr">
         <is>
           <t>PDMDEP-33362</t>
         </is>
       </c>
-      <c r="M100" s="14" t="inlineStr">
+      <c r="M108" s="14" t="inlineStr">
         <is>
           <t>00167140</t>
         </is>
       </c>
-      <c r="N100" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O100" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="17" t="inlineStr">
+      <c r="N108" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B101" s="17" t="inlineStr"/>
-      <c r="C101" s="17" t="inlineStr"/>
-      <c r="D101" s="17" t="inlineStr"/>
-      <c r="E101" s="17" t="inlineStr"/>
-      <c r="F101" s="17" t="inlineStr"/>
-      <c r="G101" s="17" t="inlineStr"/>
-      <c r="H101" s="17" t="inlineStr"/>
-      <c r="I101" s="17" t="inlineStr"/>
-      <c r="J101" s="17" t="inlineStr"/>
-      <c r="K101" s="17" t="inlineStr"/>
-      <c r="L101" s="17" t="inlineStr"/>
-      <c r="M101" s="17" t="inlineStr"/>
-      <c r="N101" s="18" t="n">
+      <c r="B109" s="17" t="inlineStr"/>
+      <c r="C109" s="17" t="inlineStr"/>
+      <c r="D109" s="17" t="inlineStr"/>
+      <c r="E109" s="17" t="inlineStr"/>
+      <c r="F109" s="17" t="inlineStr"/>
+      <c r="G109" s="17" t="inlineStr"/>
+      <c r="H109" s="17" t="inlineStr"/>
+      <c r="I109" s="17" t="inlineStr"/>
+      <c r="J109" s="17" t="inlineStr"/>
+      <c r="K109" s="17" t="inlineStr"/>
+      <c r="L109" s="17" t="inlineStr"/>
+      <c r="M109" s="17" t="inlineStr"/>
+      <c r="N109" s="18" t="n">
         <v>47526.995</v>
       </c>
-      <c r="O101" s="18" t="n">
+      <c r="O109" s="18" t="n">
         <v>10954.55</v>
       </c>
-      <c r="P101" s="18" t="n">
-        <v>150.43</v>
+      <c r="P109" s="18" t="n">
+        <v>137.69</v>
       </c>
     </row>
   </sheetData>
@@ -7954,6 +8508,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId95"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId104"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8711,26 +9273,26 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>38.25</v>
+        <v>43</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>11.58</v>
+        <v>13.58</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>5.75</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>55.58</v>
+        <v>62.33</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>7.17</v>
+        <v>10.67</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>652.05</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>9.6%</t>
         </is>
       </c>
     </row>
@@ -8772,7 +9334,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>37.5</v>
+        <v>38.25</v>
       </c>
     </row>
   </sheetData>
@@ -8936,17 +9498,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -8960,7 +9522,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 9 commande(s)</t>
+          <t>Épics créées ce mois — 10 commande(s)</t>
         </is>
       </c>
     </row>
@@ -9015,22 +9577,22 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35532</t>
+          <t>PDMDEP-35587</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35518</t>
+          <t>PDMDEP-35583</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE PRIVAS</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -9040,34 +9602,42 @@
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
-        </is>
-      </c>
-      <c r="G5" s="14" t="inlineStr"/>
-      <c r="H5" s="14" t="inlineStr"/>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>00180931</t>
+        </is>
+      </c>
       <c r="I5" s="25" t="n">
-        <v>1450</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35478</t>
+          <t>PDMDEP-35532</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35469</t>
+          <t>PDMDEP-35518</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VENCE</t>
+          <t>COMMUNE DE PRIVAS</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -9080,39 +9650,31 @@
           <t>Migration</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="inlineStr">
-        <is>
-          <t>00180643</t>
-        </is>
-      </c>
+      <c r="G6" s="11" t="inlineStr"/>
+      <c r="H6" s="11" t="inlineStr"/>
       <c r="I6" s="26" t="n">
-        <v>6285</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35410</t>
+          <t>PDMDEP-35478</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35401</t>
+          <t>PDMDEP-35469</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
+          <t>COMMUNE DE VENCE</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -9132,22 +9694,22 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>00173074</t>
+          <t>00180643</t>
         </is>
       </c>
       <c r="I7" s="25" t="n">
-        <v>1200</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35392</t>
+          <t>PDMDEP-35410</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35385</t>
+          <t>PDMDEP-35401</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -9157,7 +9719,7 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ROUEN</t>
+          <t xml:space="preserve">Commune de Saint Cast le Guildo </t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -9177,42 +9739,42 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>00179700</t>
+          <t>00173074</t>
         </is>
       </c>
       <c r="I8" s="26" t="n">
-        <v>28915.01</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35576</t>
+          <t>PDMDEP-35392</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35572</t>
+          <t>PDMDEP-35385</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)</t>
+          <t>COMMUNE DE ROUEN</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -9222,22 +9784,22 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>00180891</t>
+          <t>00179700</t>
         </is>
       </c>
       <c r="I9" s="25" t="n">
-        <v>0</v>
+        <v>28915.01</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35567</t>
+          <t>PDMDEP-35576</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35561</t>
+          <t>PDMDEP-35572</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -9247,7 +9809,7 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ARIEGE (CD 09)</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -9267,7 +9829,7 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>00180878</t>
+          <t>00180891</t>
         </is>
       </c>
       <c r="I10" s="26" t="n">
@@ -9277,22 +9839,22 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35511</t>
+          <t>PDMDEP-35567</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35504</t>
+          <t>PDMDEP-35561</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>[TEST]</t>
+          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -9302,7 +9864,7 @@
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -9312,7 +9874,7 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>0015489263</t>
+          <t>00180878</t>
         </is>
       </c>
       <c r="I11" s="25" t="n">
@@ -9322,22 +9884,22 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35464</t>
+          <t>PDMDEP-35511</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35460</t>
+          <t>PDMDEP-35504</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
+          <t>[TEST]</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -9347,7 +9909,7 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
@@ -9357,83 +9919,107 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>00180631</t>
+          <t>0015489263</t>
         </is>
       </c>
       <c r="I12" s="26" t="n">
-        <v>455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
+          <t>PDMDEP-35464</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35460</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>00180631</t>
+        </is>
+      </c>
+      <c r="I13" s="25" t="n">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
           <t>PDMDEP-35439</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-35435</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>03/09/2026</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr">
+      <c r="H14" s="11" t="inlineStr">
         <is>
           <t>00180506</t>
         </is>
       </c>
-      <c r="I13" s="25" t="n">
+      <c r="I14" s="26" t="n">
         <v>3974</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="n"/>
-      <c r="C14" s="17" t="n"/>
-      <c r="D14" s="17" t="n"/>
-      <c r="E14" s="17" t="n"/>
-      <c r="F14" s="17" t="n"/>
-      <c r="G14" s="17" t="n"/>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>9 commande(s)</t>
-        </is>
-      </c>
-      <c r="I14" s="24" t="n">
-        <v>42279</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B15" s="17" t="n"/>
@@ -9444,17 +10030,17 @@
       <c r="G15" s="17" t="n"/>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>5 commande(s)</t>
+          <t>10 commande(s)</t>
         </is>
       </c>
       <c r="I15" s="24" t="n">
-        <v>4429</v>
+        <v>42279</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B16" s="17" t="n"/>
@@ -9465,10 +10051,31 @@
       <c r="G16" s="17" t="n"/>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>4 commande(s)</t>
+          <t>5 commande(s)</t>
         </is>
       </c>
       <c r="I16" s="24" t="n">
+        <v>4429</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
+      <c r="G17" s="17" t="n"/>
+      <c r="H17" s="17" t="inlineStr">
+        <is>
+          <t>5 commande(s)</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="n">
         <v>37850</v>
       </c>
     </row>
